--- a/data/trans_dic/P32A-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P32A-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le ha molestado que le criticasen la forma de beber</t>
+          <t>Población a la que le ha molestado que le criticasen la forma de beber (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -722,57 +722,57 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 5,97</t>
+          <t>1,7; 6,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,94</t>
+          <t>0,44; 4,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,38</t>
+          <t>0,0; 3,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,84</t>
+          <t>0,55; 5,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 13,49</t>
+          <t>0,35; 12,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>0,0; 1,55</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,08</t>
+          <t>1,39; 4,08</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,24</t>
+          <t>0,58; 3,36</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 5,26</t>
+          <t>0,12; 5,25</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,11</t>
+          <t>0,39; 2,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,6</t>
+          <t>1,69; 4,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,54; 5,19</t>
+          <t>1,45; 5,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,27</t>
+          <t>0,0; 3,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,59</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,22</t>
+          <t>0,0; 2,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,95</t>
+          <t>0,0; 2,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,94</t>
+          <t>0,0; 3,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,82</t>
+          <t>0,28; 1,79</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,44</t>
+          <t>1,21; 3,55</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,64</t>
+          <t>1,07; 3,54</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,59</t>
+          <t>0,22; 2,51</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,8</t>
+          <t>0,46; 2,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 5,64</t>
+          <t>1,46; 4,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,65</t>
+          <t>0,91; 3,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 2,99</t>
+          <t>0,06; 2,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,09</t>
+          <t>0,0; 2,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,93</t>
+          <t>0,0; 2,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,68</t>
+          <t>0,0; 2,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,73</t>
+          <t>0,29; 3,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,32</t>
+          <t>0,45; 2,02</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,43</t>
+          <t>1,1; 3,5</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,78</t>
+          <t>0,86; 2,79</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,43</t>
+          <t>0,38; 2,11</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,03</t>
+          <t>0,0; 2,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,85</t>
+          <t>1,0; 4,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,17</t>
+          <t>0,93; 4,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,32</t>
+          <t>0,95; 4,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,73</t>
+          <t>0,0; 2,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,54</t>
+          <t>0,0; 2,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 2,8</t>
+          <t>0,17; 2,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,36</t>
+          <t>0,0; 1,57</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,34</t>
+          <t>0,72; 3,61</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,78</t>
+          <t>0,73; 2,86</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,08</t>
+          <t>0,8; 3,2</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 6,23</t>
+          <t>1,37; 7,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,76</t>
+          <t>0,0; 4,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,46</t>
+          <t>0,76; 4,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,98; 6,39</t>
+          <t>2,2; 6,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 10,78</t>
+          <t>0,91; 11,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 8,73</t>
+          <t>0,86; 9,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,88</t>
+          <t>0,84; 4,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,71; 5,04</t>
+          <t>0,77; 5,1</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,33</t>
+          <t>0,35; 4,36</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,08; 4,69</t>
+          <t>1,1; 4,53</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,92</t>
+          <t>1,96; 5,0</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,29</t>
+          <t>0,61; 5,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,33</t>
+          <t>0,51; 4,4</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,78</t>
+          <t>1,1; 4,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,76</t>
+          <t>0,0; 8,33</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>0,0; 2,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,8</t>
+          <t>0,44; 3,92</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,06</t>
+          <t>0,43; 3,71</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,81</t>
+          <t>0,26; 2,82</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,98</t>
+          <t>0,0; 6,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,42</t>
+          <t>0,0; 11,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 6,19</t>
+          <t>0,69; 6,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,84</t>
+          <t>0,0; 16,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,67</t>
+          <t>0,0; 8,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,57</t>
+          <t>0,0; 6,32</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,25</t>
+          <t>0,0; 11,05</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,28</t>
+          <t>0,0; 4,55</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,16</t>
+          <t>0,91; 5,03</t>
         </is>
       </c>
     </row>
@@ -1697,22 +1697,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,65</t>
+          <t>0,64; 1,59</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,41</t>
+          <t>1,88; 3,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,36; 2,7</t>
+          <t>1,44; 2,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,46</t>
+          <t>1,23; 2,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1722,37 +1722,37 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,68</t>
+          <t>0,39; 1,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,3</t>
+          <t>0,77; 2,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,4</t>
+          <t>0,59; 2,37</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,23</t>
+          <t>0,55; 1,27</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,6</t>
+          <t>1,46; 2,54</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,24</t>
+          <t>1,31; 2,26</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,18</t>
+          <t>1,1; 2,14</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le ha molestado que le criticasen la forma de beber</t>
+          <t>Población a la que le ha molestado que le criticasen la forma de beber (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6991</t>
+          <t>0; 6990</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4639; 16696</t>
+          <t>4760; 16777</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1114; 10052</t>
+          <t>1114; 10311</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4582</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1816</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 6208</t>
+          <t>0; 7149</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>937; 8351</t>
+          <t>945; 8738</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>461; 13369</t>
+          <t>346; 12461</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 6909</t>
+          <t>0; 7238</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6391; 18909</t>
+          <t>6423; 18882</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2276; 13837</t>
+          <t>2473; 14355</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>508; 14156</t>
+          <t>330; 14114</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1939; 10567</t>
+          <t>1952; 10946</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7385; 21511</t>
+          <t>7889; 21975</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5619; 18985</t>
+          <t>5293; 18916</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 7515</t>
+          <t>0; 8085</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5599</t>
+          <t>0; 5615</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4690</t>
+          <t>0; 5367</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6627</t>
+          <t>0; 6557</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5541</t>
+          <t>0; 5435</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2173; 13066</t>
+          <t>2030; 12866</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8304; 23396</t>
+          <t>8210; 24078</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6255; 21484</t>
+          <t>6336; 20898</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>873; 9608</t>
+          <t>831; 9296</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1914; 11262</t>
+          <t>1845; 10576</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6866; 24052</t>
+          <t>6236; 21244</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4202; 15784</t>
+          <t>3946; 16427</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>166; 8404</t>
+          <t>166; 8260</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6935</t>
+          <t>0; 5914</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4686</t>
+          <t>0; 5751</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 6678</t>
+          <t>0; 5803</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>438; 5599</t>
+          <t>440; 5527</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2822; 14502</t>
+          <t>2793; 12672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7325; 22942</t>
+          <t>7340; 23449</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5797; 18949</t>
+          <t>5838; 19019</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1719; 10478</t>
+          <t>1660; 9095</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6353</t>
+          <t>0; 8397</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3996; 18953</t>
+          <t>3924; 19071</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3423; 16211</t>
+          <t>3622; 17775</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3304; 14700</t>
+          <t>3240; 13891</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1989</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5827</t>
+          <t>0; 5210</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 6765</t>
+          <t>0; 7721</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>162; 5277</t>
+          <t>312; 4262</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 6257</t>
+          <t>0; 7189</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4428; 20181</t>
+          <t>4326; 21813</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4989; 18236</t>
+          <t>4792; 18730</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4296; 16287</t>
+          <t>4206; 16892</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1679; 11223</t>
+          <t>2460; 12908</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 11036</t>
+          <t>0; 11021</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2226; 12776</t>
+          <t>2192; 12367</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5197; 16790</t>
+          <t>5774; 17368</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 1926</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1007; 12094</t>
+          <t>1025; 12828</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1115; 11305</t>
+          <t>1110; 11767</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1121; 6582</t>
+          <t>1125; 6542</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1811; 12871</t>
+          <t>1968; 13023</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1889; 14889</t>
+          <t>1205; 15004</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4492; 19517</t>
+          <t>4559; 18862</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7764; 19568</t>
+          <t>7783; 19881</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1858</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>937; 8126</t>
+          <t>937; 8432</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>899; 7683</t>
+          <t>901; 7808</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1923; 9050</t>
+          <t>2091; 8589</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 1752</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 2119</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 5152</t>
+          <t>0; 5530</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 6382</t>
+          <t>0; 6669</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 1851</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>919; 7971</t>
+          <t>925; 8237</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1018; 9896</t>
+          <t>1060; 9059</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>978; 13172</t>
+          <t>1227; 13215</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 5108</t>
+          <t>0; 5062</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 10623</t>
+          <t>0; 9716</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 1648</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>572; 6196</t>
+          <t>694; 6317</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 2083</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 2015</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 5795</t>
+          <t>0; 6028</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 2320</t>
+          <t>0; 2242</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 4996</t>
+          <t>0; 5670</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 12360</t>
+          <t>0; 12142</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 6975</t>
+          <t>0; 6010</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1133; 6544</t>
+          <t>1148; 6377</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>12904; 30978</t>
+          <t>11965; 29959</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>37804; 69413</t>
+          <t>38180; 69394</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>27273; 54016</t>
+          <t>28847; 55342</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>19920; 38761</t>
+          <t>19406; 39309</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>924; 7924</t>
+          <t>920; 7988</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4015; 17596</t>
+          <t>4072; 18124</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8583; 26333</t>
+          <t>8814; 24966</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>6208; 24462</t>
+          <t>6027; 24138</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>15185; 34160</t>
+          <t>15277; 35166</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>44321; 79962</t>
+          <t>45046; 78254</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>41469; 70542</t>
+          <t>41155; 71005</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>29711; 56615</t>
+          <t>28537; 55541</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32A-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P32A-Edad-trans_dic.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,49</t>
+          <t>0,0; 2,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,7; 6,0</t>
+          <t>1,64; 5,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,04</t>
+          <t>0,43; 3,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -742,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,9</t>
+          <t>0,0; 3,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,07</t>
+          <t>0,54; 4,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 12,58</t>
+          <t>2,0; 16,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,55</t>
+          <t>0,0; 1,54</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,08</t>
+          <t>1,38; 4,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,36</t>
+          <t>0,59; 3,34</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 5,25</t>
+          <t>0,84; 7,41</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,18</t>
+          <t>0,39; 2,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,7</t>
+          <t>1,62; 4,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 5,17</t>
+          <t>1,39; 5,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,51</t>
+          <t>0,0; 2,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,0; 2,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,54</t>
+          <t>0,0; 2,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,92</t>
+          <t>0,0; 3,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,86</t>
+          <t>0,0; 4,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,79</t>
+          <t>0,28; 1,65</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,55</t>
+          <t>1,23; 3,32</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,54</t>
+          <t>1,11; 3,5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,51</t>
+          <t>0,21; 2,03</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,63</t>
+          <t>0,46; 2,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,98</t>
+          <t>1,61; 5,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,8</t>
+          <t>1,05; 3,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 2,94</t>
+          <t>0,36; 2,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,64</t>
+          <t>0,0; 3,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 2,11</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>0,0; 2,36</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,33</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,68</t>
+          <t>0,27; 3,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,02</t>
+          <t>0,45; 2,14</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,5</t>
+          <t>1,15; 3,44</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,79</t>
+          <t>0,85; 2,74</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,11</t>
+          <t>0,41; 2,58</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,68</t>
+          <t>0,0; 2,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,88</t>
+          <t>1,0; 4,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,57</t>
+          <t>0,9; 4,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,08</t>
+          <t>1,1; 4,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,44</t>
+          <t>0,0; 2,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1172,27 +1172,27 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,26</t>
+          <t>0,33; 2,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,57</t>
+          <t>0,0; 1,38</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,61</t>
+          <t>0,73; 3,25</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,86</t>
+          <t>0,77; 3,08</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,2</t>
+          <t>0,94; 3,32</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -1277,22 +1277,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 7,17</t>
+          <t>1,03; 7,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,75</t>
+          <t>0,0; 5,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,31</t>
+          <t>0,78; 4,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,2; 6,61</t>
+          <t>1,91; 5,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1302,37 +1302,37 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 11,43</t>
+          <t>0,9; 10,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 9,08</t>
+          <t>0,85; 8,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,85</t>
+          <t>0,79; 4,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,77; 5,1</t>
+          <t>0,76; 5,19</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 4,36</t>
+          <t>0,56; 4,99</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,53</t>
+          <t>1,07; 4,71</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,96; 5,0</t>
+          <t>1,73; 4,69</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -1422,17 +1422,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,49</t>
+          <t>0,61; 5,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,4</t>
+          <t>0,5; 4,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,54</t>
+          <t>1,08; 4,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,33</t>
+          <t>0,0; 8,7</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,39</t>
+          <t>0,54; 4,48</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1462,17 +1462,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,92</t>
+          <t>0,45; 3,77</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,71</t>
+          <t>0,4; 3,95</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,82</t>
+          <t>1,19; 4,27</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,92</t>
+          <t>0,0; 6,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,36</t>
+          <t>0,0; 13,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,32</t>
+          <t>0,52; 5,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1587,32 +1587,32 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,48</t>
+          <t>0,0; 15,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,38</t>
+          <t>0,0; 12,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,32</t>
+          <t>0,0; 6,16</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,05</t>
+          <t>0,0; 10,1</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,55</t>
+          <t>0,0; 5,71</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,03</t>
+          <t>0,89; 5,21</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,59</t>
+          <t>0,66; 1,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,88; 3,41</t>
+          <t>1,92; 3,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,77</t>
+          <t>1,39; 2,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,5</t>
+          <t>1,26; 2,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,89</t>
+          <t>0,1; 0,9</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,74</t>
+          <t>0,37; 1,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,18</t>
+          <t>0,73; 2,16</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,37</t>
+          <t>1,3; 3,44</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,27</t>
+          <t>0,55; 1,28</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,54</t>
+          <t>1,5; 2,61</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,26</t>
+          <t>1,29; 2,28</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,14</t>
+          <t>1,48; 2,55</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4164</t>
+          <t>7843</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4164</t>
+          <t>7843</t>
         </is>
       </c>
     </row>
@@ -2068,17 +2068,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6990</t>
+          <t>0; 6755</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4760; 16777</t>
+          <t>4585; 16706</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1114; 10311</t>
+          <t>1099; 9840</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2093,37 +2093,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 7149</t>
+          <t>0; 7077</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>945; 8738</t>
+          <t>936; 8371</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>346; 12461</t>
+          <t>2223; 17904</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 7238</t>
+          <t>0; 7178</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6423; 18882</t>
+          <t>6407; 19074</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2473; 14355</t>
+          <t>2524; 14280</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>330; 14114</t>
+          <t>2324; 20547</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1558</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1751</t>
+          <t>1778</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3309</t>
+          <t>3014</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1952; 10946</t>
+          <t>1939; 10684</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7889; 21975</t>
+          <t>7560; 21040</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5293; 18916</t>
+          <t>5084; 18905</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 8085</t>
+          <t>0; 6425</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5615</t>
+          <t>0; 5113</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5367</t>
+          <t>0; 4523</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6557</t>
+          <t>0; 6736</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5435</t>
+          <t>0; 6428</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2030; 12866</t>
+          <t>1977; 11853</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8210; 24078</t>
+          <t>8370; 22559</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6336; 20898</t>
+          <t>6535; 20658</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>831; 9296</t>
+          <t>833; 8155</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3452</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>2087</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>5539</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1845; 10576</t>
+          <t>1830; 11064</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6236; 21244</t>
+          <t>6879; 22978</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3946; 16427</t>
+          <t>4550; 16513</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>166; 8260</t>
+          <t>1123; 9255</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5914</t>
+          <t>0; 6799</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5751</t>
+          <t>0; 5127</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5803</t>
+          <t>0; 5895</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>440; 5527</t>
+          <t>460; 5707</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2793; 12672</t>
+          <t>2825; 13415</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7340; 23449</t>
+          <t>7730; 23023</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5838; 19019</t>
+          <t>5817; 18667</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1660; 9095</t>
+          <t>1980; 12424</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7422</t>
+          <t>8291</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8899</t>
+          <t>10402</t>
         </is>
       </c>
     </row>
@@ -2692,22 +2692,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 8397</t>
+          <t>0; 7377</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3924; 19071</t>
+          <t>3927; 18232</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3622; 17775</t>
+          <t>3493; 17030</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3240; 13891</t>
+          <t>3854; 15657</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2717,37 +2717,37 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5210</t>
+          <t>0; 5267</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 7721</t>
+          <t>0; 7722</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>312; 4262</t>
+          <t>690; 5620</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 7189</t>
+          <t>0; 6314</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4326; 21813</t>
+          <t>4399; 19649</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4792; 18730</t>
+          <t>5013; 20148</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4206; 16892</t>
+          <t>5236; 18529</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9846</t>
+          <t>9703</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2915</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12761</t>
+          <t>12827</t>
         </is>
       </c>
     </row>
@@ -2900,22 +2900,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2460; 12908</t>
+          <t>1848; 12825</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 11021</t>
+          <t>0; 13463</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2192; 12367</t>
+          <t>2229; 12351</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5774; 17368</t>
+          <t>5334; 16151</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2925,37 +2925,37 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1025; 12828</t>
+          <t>1012; 11218</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1110; 11767</t>
+          <t>1103; 10985</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1125; 6542</t>
+          <t>1169; 7280</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1968; 13023</t>
+          <t>1940; 13265</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1205; 15004</t>
+          <t>1916; 17159</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4559; 18862</t>
+          <t>4469; 19589</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7783; 19881</t>
+          <t>7401; 20020</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5708</t>
+          <t>6628</t>
         </is>
       </c>
     </row>
@@ -3113,17 +3113,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>937; 8432</t>
+          <t>932; 7787</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>901; 7808</t>
+          <t>889; 8156</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2091; 8589</t>
+          <t>2226; 10139</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 5530</t>
+          <t>0; 5776</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 6669</t>
+          <t>429; 3532</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3153,17 +3153,17 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>925; 8237</t>
+          <t>943; 7921</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1060; 9059</t>
+          <t>971; 9641</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1227; 13215</t>
+          <t>3394; 12210</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>3556</t>
         </is>
       </c>
     </row>
@@ -3316,12 +3316,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 5062</t>
+          <t>0; 5071</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 9716</t>
+          <t>0; 11417</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>694; 6317</t>
+          <t>568; 5850</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3346,32 +3346,32 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 6028</t>
+          <t>0; 5756</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 2242</t>
+          <t>0; 3985</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 5670</t>
+          <t>0; 5525</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 12142</t>
+          <t>0; 11099</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 6010</t>
+          <t>0; 7532</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1148; 6377</t>
+          <t>1246; 7315</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>27988</t>
+          <t>30436</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>14096</t>
+          <t>19375</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>42084</t>
+          <t>49810</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>11965; 29959</t>
+          <t>12346; 29693</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>38180; 69394</t>
+          <t>39128; 70569</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>28847; 55342</t>
+          <t>27913; 53413</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>19406; 39309</t>
+          <t>21105; 42024</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>920; 7988</t>
+          <t>924; 8006</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4072; 18124</t>
+          <t>3822; 17226</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8814; 24966</t>
+          <t>8363; 24760</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>6027; 24138</t>
+          <t>11687; 30924</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>15277; 35166</t>
+          <t>15380; 35509</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>45046; 78254</t>
+          <t>46237; 80252</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>41155; 71005</t>
+          <t>40566; 71659</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>28537; 55541</t>
+          <t>37978; 65653</t>
         </is>
       </c>
     </row>
